--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q10_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000728974139684789</v>
+        <v>0.0002397291899174862</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000728974139684789</v>
+        <v>0.0002397291899174862</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005734608578590033</v>
+        <v>0.0002428830333654625</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0007232786416722125</v>
+        <v>0.0002369887044551563</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007232786416722125</v>
+        <v>0.0002369887044551563</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005365946905431419</v>
+        <v>0.0002385334305865696</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0007118393553205437</v>
+        <v>0.0002320547220539381</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007118393553205437</v>
+        <v>0.0002320547220539381</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004964573220837572</v>
+        <v>0.0002340353765352412</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0006919896756267485</v>
+        <v>0.0002242998494169446</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0006919896756267485</v>
+        <v>0.0002242998494169446</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004586393711173532</v>
+        <v>0.0002283121478397375</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0006717447979677396</v>
+        <v>0.0002166491519988439</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006717447979677396</v>
+        <v>0.0002166491519988439</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004238284816579342</v>
+        <v>0.0002209645081891726</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0006562763484625918</v>
+        <v>0.0002109519050032894</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0006562763484625918</v>
+        <v>0.0002109519050032894</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003937286339056664</v>
+        <v>0.0002131152773294117</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0006479278447095094</v>
+        <v>0.0002079882557036276</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006479278447095094</v>
+        <v>0.0002079882557036276</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0003698546797004579</v>
+        <v>0.0002059293444553234</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0006493497086999646</v>
+        <v>0.0002085969543977473</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0006493497086999646</v>
+        <v>0.0002085969543977473</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0003558165536373965</v>
+        <v>0.000200948638825924</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0006580097188543752</v>
+        <v>0.0002119026123531996</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0006580097188543752</v>
+        <v>0.0002119026123531996</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0003551579508671818</v>
+        <v>0.0002014886823824574</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.000691070736807261</v>
+        <v>0.0002234729002282096</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000691070736807261</v>
+        <v>0.0002234729002282096</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00036998321959718</v>
+        <v>0.0002085753183168981</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0007378130715821805</v>
+        <v>0.0002397462700792596</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007378130715821805</v>
+        <v>0.0002397462700792596</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0003991790588149667</v>
+        <v>0.0002233690321771579</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0008045189123250158</v>
+        <v>0.0002627435369460396</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0008045189123250158</v>
+        <v>0.0002627435369460396</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0004402116369926989</v>
+        <v>0.0002453557430593991</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0008964519878297354</v>
+        <v>0.0002941687183948657</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0008964519878297354</v>
+        <v>0.0002941687183948657</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004899764116600892</v>
+        <v>0.0002737711809967537</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001005705572806377</v>
+        <v>0.000331344976906647</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001005705572806377</v>
+        <v>0.000331344976906647</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0005469216785287652</v>
+        <v>0.0003083606123714109</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00113449691311129</v>
+        <v>0.0003749397895405272</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00113449691311129</v>
+        <v>0.0003749397895405272</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0006103719051185226</v>
+        <v>0.0003487683387502158</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.001279076145953896</v>
+        <v>0.000423622983049932</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001279076145953896</v>
+        <v>0.000423622983049932</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000680564800422238</v>
+        <v>0.0003947189537474887</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001433042875054445</v>
+        <v>0.0004751603612282622</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001433042875054445</v>
+        <v>0.0004751603612282622</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0007605010348289256</v>
+        <v>0.0004456320640403531</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.001598795272442461</v>
+        <v>0.0005302512495716377</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001598795272442461</v>
+        <v>0.0005302512495716377</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0008510537093427425</v>
+        <v>0.0005003985572718922</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001772006977858232</v>
+        <v>0.0005874009435214964</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001772006977858232</v>
+        <v>0.0005874009435214964</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000945515994254613</v>
+        <v>0.0005575861830143317</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00194374875805966</v>
+        <v>0.0006436228086272199</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00194374875805966</v>
+        <v>0.0006436228086272199</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001035032727568907</v>
+        <v>0.0006111114631900201</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.002109991148619902</v>
+        <v>0.00069764778853924</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002109991148619902</v>
+        <v>0.00069764778853924</v>
       </c>
       <c r="D22" t="n">
-        <v>0.001105938297071819</v>
+        <v>0.0006575991364865326</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002272442127182697</v>
+        <v>0.0007501881711661192</v>
       </c>
       <c r="C23" t="n">
-        <v>0.002272442127182697</v>
+        <v>0.0007501881711661192</v>
       </c>
       <c r="D23" t="n">
-        <v>0.001163438305652391</v>
+        <v>0.0006958331583998534</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.002442189598236325</v>
+        <v>0.0008051000975473464</v>
       </c>
       <c r="C24" t="n">
-        <v>0.002442189598236325</v>
+        <v>0.0008051000975473464</v>
       </c>
       <c r="D24" t="n">
-        <v>0.001225337078648415</v>
+        <v>0.0007327118392973613</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.002627410328230957</v>
+        <v>0.0008653428554008377</v>
       </c>
       <c r="C25" t="n">
-        <v>0.002627410328230957</v>
+        <v>0.0008653428554008377</v>
       </c>
       <c r="D25" t="n">
-        <v>0.001308036342409909</v>
+        <v>0.0007751846981324525</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002835349207015956</v>
+        <v>0.0009334632628987514</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002835349207015956</v>
+        <v>0.0009334632628987514</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001417239791468392</v>
+        <v>0.0008266888853271392</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.003060953841787655</v>
+        <v>0.001007809228774843</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003060953841787655</v>
+        <v>0.001007809228774843</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00154679850160895</v>
+        <v>0.0008863920739312642</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.003301322324512095</v>
+        <v>0.001087478983287049</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003301322324512095</v>
+        <v>0.001087478983287049</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001687293332523855</v>
+        <v>0.000952992857358108</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.00354673217829317</v>
+        <v>0.001169161310884839</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00354673217829317</v>
+        <v>0.001169161310884839</v>
       </c>
       <c r="D29" t="n">
-        <v>0.001828285736574707</v>
+        <v>0.001022681463646878</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003786917909200506</v>
+        <v>0.001249305723386667</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003786917909200506</v>
+        <v>0.001249305723386667</v>
       </c>
       <c r="D30" t="n">
-        <v>0.001959972275582936</v>
+        <v>0.001091595719994056</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.004020725972360691</v>
+        <v>0.001327439577784085</v>
       </c>
       <c r="C31" t="n">
-        <v>0.004020725972360691</v>
+        <v>0.001327439577784085</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002079142483470785</v>
+        <v>0.001157978975580968</v>
       </c>
     </row>
   </sheetData>
